--- a/src/main/resources/espacios/2 Step/0 - Verbos.xlsx
+++ b/src/main/resources/espacios/2 Step/0 - Verbos.xlsx
@@ -14547,13 +14547,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F797"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.55"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="33.89"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25617,7 +25617,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F808"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.55"/>
